--- a/data/trans_orig/P1425-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2007</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675004</t>
+          <t>674039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688223</t>
+          <t>687421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>671246</t>
+          <t>671385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>683844</t>
+          <t>684242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351553</t>
+          <t>1350544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1369078</t>
+          <t>1368941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>37851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>938004</t>
+          <t>938768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>954328</t>
+          <t>954540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>945573</t>
+          <t>945526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961426</t>
+          <t>961347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1891505</t>
+          <t>1892342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1912224</t>
+          <t>1912422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664069</t>
+          <t>665851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675594</t>
+          <t>675585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>671455</t>
+          <t>670167</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681081</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1340821</t>
+          <t>1341394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1354748</t>
+          <t>1354794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924299</t>
+          <t>924696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937928</t>
+          <t>937938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023705</t>
+          <t>1023767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952925</t>
+          <t>1953257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970452</t>
+          <t>1971125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54004</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,82 +2119,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>36848</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24563</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>77580</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>61383</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>97777</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50834</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>77580</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>61588</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>95599</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3222539</t>
+          <t>3222225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3246442</t>
+          <t>3246849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,82 +2232,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3342349</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3329195</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3354634</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6578161</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6557964</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6594358</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3261</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3342349</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3328363</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3353040</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6578161</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6560142</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6594153</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2012</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>690243</t>
+          <t>690476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701468</t>
+          <t>700624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>688873</t>
+          <t>688234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696090</t>
+          <t>696100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1383668</t>
+          <t>1384573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1396518</t>
+          <t>1396498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,82 +3037,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16278</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>19684</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>12157</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>30844</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3281</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16634</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>19684</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>12261</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>30155</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998875</t>
+          <t>998470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011920</t>
+          <t>1012651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,82 +3150,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1020601</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1012695</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1025641</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2027237</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2016077</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2034764</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1020601</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1012339</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1025692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2027237</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2016766</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2034660</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738959</t>
+          <t>739612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754585</t>
+          <t>754570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768762</t>
+          <t>767702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776190</t>
+          <t>776194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1512374</t>
+          <t>1511986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529431</t>
+          <t>1529396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929940</t>
+          <t>930184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945546</t>
+          <t>945608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1036303</t>
+          <t>1037025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049048</t>
+          <t>1049133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1975090</t>
+          <t>1974237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1993273</t>
+          <t>1992529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73422</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3379228</t>
+          <t>3379433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3404801</t>
+          <t>3404196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3522573</t>
+          <t>3521051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3541758</t>
+          <t>3541752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6908455</t>
+          <t>6910423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6941237</t>
+          <t>6942185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2016</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20502</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659336</t>
+          <t>660044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671104</t>
+          <t>671617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660708</t>
+          <t>661151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671640</t>
+          <t>671638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1327137</t>
+          <t>1325561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340924</t>
+          <t>1341134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006812</t>
+          <t>1007023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1019240</t>
+          <t>1019204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1031408</t>
+          <t>1030935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1040962</t>
+          <t>1040933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2043639</t>
+          <t>2043643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2058175</t>
+          <t>2058084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747885</t>
+          <t>747379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757575</t>
+          <t>757558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768785</t>
+          <t>769688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781753</t>
+          <t>782569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521936</t>
+          <t>1521413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1538195</t>
+          <t>1537521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>26098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,47 +5705,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>26609</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>38544</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>26609</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>17548</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>40089</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918696</t>
+          <t>917802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932373</t>
+          <t>932413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1016791</t>
+          <t>1017681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034720</t>
+          <t>1035135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,47 +5818,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1954737</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1942802</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1964048</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,13%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1954737</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1941257</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1963798</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3350710</t>
+          <t>3349054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373070</t>
+          <t>3371866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3496845</t>
+          <t>3496821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3520952</t>
+          <t>3521891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6855326</t>
+          <t>6853082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6888598</t>
+          <t>6889664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1425-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>30779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674039</t>
+          <t>674937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687421</t>
+          <t>687975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>671385</t>
+          <t>670705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>684242</t>
+          <t>683520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1350544</t>
+          <t>1351584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1368941</t>
+          <t>1369452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,49 +1090,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7239</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23146</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13404</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7046</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22867</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>39815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>938768</t>
+          <t>939779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>954540</t>
+          <t>954638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,49 +1203,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>954989</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>945247</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>961154</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>97,61%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>954989</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>945526</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>961347</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1778</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1892342</t>
+          <t>1890378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1912422</t>
+          <t>1913021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665851</t>
+          <t>665221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675585</t>
+          <t>675607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670167</t>
+          <t>670052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>680749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1341394</t>
+          <t>1339689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1354794</t>
+          <t>1354887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924696</t>
+          <t>924675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937938</t>
+          <t>937904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023767</t>
+          <t>1023549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035430</t>
+          <t>1035337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1953257</t>
+          <t>1953498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971125</t>
+          <t>1971433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61383</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3222225</t>
+          <t>3222640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3246849</t>
+          <t>3247132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3329195</t>
+          <t>3327589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3354634</t>
+          <t>3353028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6557964</t>
+          <t>6559168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6594358</t>
+          <t>6592790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>690476</t>
+          <t>691857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700624</t>
+          <t>701467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>688234</t>
+          <t>688675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696100</t>
+          <t>696085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1384573</t>
+          <t>1384621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1396498</t>
+          <t>1396469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998470</t>
+          <t>996499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012651</t>
+          <t>1011723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012695</t>
+          <t>1012859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025641</t>
+          <t>1025626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2016077</t>
+          <t>2016540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2034764</t>
+          <t>2035127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739612</t>
+          <t>738718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754570</t>
+          <t>754631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>767702</t>
+          <t>767485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776194</t>
+          <t>776183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1511986</t>
+          <t>1511366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529396</t>
+          <t>1528799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930184</t>
+          <t>929753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945608</t>
+          <t>945533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1037025</t>
+          <t>1036914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049133</t>
+          <t>1049096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1974237</t>
+          <t>1973711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1992529</t>
+          <t>1992000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3379433</t>
+          <t>3379227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3404196</t>
+          <t>3404052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3521051</t>
+          <t>3521334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3541752</t>
+          <t>3541640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6910423</t>
+          <t>6908498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6942185</t>
+          <t>6940359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660044</t>
+          <t>659316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671617</t>
+          <t>671059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661151</t>
+          <t>661020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325561</t>
+          <t>1325578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1341134</t>
+          <t>1340821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007023</t>
+          <t>1006988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1019204</t>
+          <t>1018417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1030935</t>
+          <t>1031626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1040933</t>
+          <t>1040952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2043643</t>
+          <t>2043169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2058084</t>
+          <t>2058171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747379</t>
+          <t>747677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757558</t>
+          <t>757635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>769688</t>
+          <t>767765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782569</t>
+          <t>782119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521413</t>
+          <t>1521648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537521</t>
+          <t>1537639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,47 +5705,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>26609</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>38999</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>26609</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>17298</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>38544</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917802</t>
+          <t>918765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932413</t>
+          <t>932197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1017681</t>
+          <t>1016209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035135</t>
+          <t>1034608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,47 +5818,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1954737</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1942347</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1964892</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1954737</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1942802</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1964048</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85810</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3349054</t>
+          <t>3349182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371866</t>
+          <t>3372394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3496821</t>
+          <t>3496635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3521891</t>
+          <t>3520930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6853082</t>
+          <t>6856588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6889664</t>
+          <t>6890056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
